--- a/reports/jobs_2026-10-11.xlsx
+++ b/reports/jobs_2026-10-11.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1397,17 +1397,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1444,17 +1444,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1462,11 +1462,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -1474,12 +1470,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1491,12 +1487,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1509,11 +1505,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -1521,12 +1513,12 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1538,12 +1530,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>AI Governance Arcitect</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1556,11 +1548,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -1568,12 +1556,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1585,17 +1573,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1611,12 +1599,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1628,12 +1616,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1646,11 +1634,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -1658,12 +1642,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1675,12 +1659,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1693,11 +1677,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -1705,12 +1685,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1722,17 +1702,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1740,11 +1720,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -1752,12 +1728,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1769,12 +1745,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1787,11 +1763,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -1799,12 +1771,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1816,17 +1788,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1836,7 +1808,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1846,12 +1818,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1863,17 +1835,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1883,7 +1855,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1893,12 +1865,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1910,17 +1882,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1930,7 +1902,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1940,12 +1912,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1957,17 +1929,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1977,7 +1949,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1987,12 +1959,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2004,17 +1976,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2022,7 +1994,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2030,12 +2006,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2047,17 +2023,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2073,12 +2049,12 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2090,12 +2066,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>AI Governance Arcitect</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2116,12 +2092,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2133,17 +2109,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2151,7 +2127,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2159,12 +2139,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2176,12 +2156,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2194,7 +2174,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2202,12 +2186,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2219,12 +2203,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2245,12 +2229,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2262,17 +2246,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2280,7 +2264,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2288,12 +2276,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2305,17 +2293,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2331,12 +2319,12 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2348,17 +2336,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2368,7 +2356,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2378,12 +2366,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2395,12 +2383,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2413,11 +2401,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2425,12 +2409,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2442,17 +2426,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2462,7 +2446,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2472,12 +2456,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2489,17 +2473,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2509,7 +2493,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2519,12 +2503,12 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2536,17 +2520,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2556,7 +2540,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2566,12 +2550,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2583,12 +2567,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2601,7 +2585,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2609,12 +2597,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2626,17 +2614,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2644,7 +2632,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2652,12 +2644,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2669,12 +2661,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2687,11 +2679,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2699,12 +2687,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2716,17 +2704,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2736,7 +2724,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2746,12 +2734,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2763,12 +2751,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2781,7 +2769,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2789,12 +2781,12 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2806,17 +2798,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2826,7 +2818,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2836,12 +2828,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2853,17 +2845,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2879,12 +2871,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2896,17 +2888,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2916,7 +2908,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2926,12 +2918,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2943,12 +2935,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2961,7 +2953,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -2969,12 +2965,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2986,17 +2982,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3006,7 +3002,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3016,12 +3012,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3033,27 +3029,27 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3063,12 +3059,12 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3080,12 +3076,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3100,7 +3096,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3110,12 +3106,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3127,17 +3123,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3147,7 +3143,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3157,12 +3153,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3174,27 +3170,27 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>Software Engineer- SaaS O365</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3204,12 +3200,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3221,17 +3217,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3239,7 +3235,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3329,11 +3329,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -3341,12 +3337,12 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3358,17 +3354,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3376,11 +3372,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -3388,12 +3380,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3405,17 +3397,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3431,12 +3423,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3448,12 +3440,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3466,11 +3458,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -3478,12 +3466,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3495,17 +3483,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3515,7 +3503,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3525,12 +3513,12 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3542,17 +3530,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3562,7 +3550,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3572,12 +3560,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3589,29 +3577,25 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>0-2 years</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bangalore </t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -3619,12 +3603,12 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3636,12 +3620,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3654,11 +3638,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -3666,12 +3646,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3683,17 +3663,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3703,7 +3683,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3713,12 +3693,12 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3730,27 +3710,27 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Thoughtworks India</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer- SaaS O365</t>
+          <t>Developer (Vapasi) - Intern</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>1–5 years</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3760,12 +3740,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3777,12 +3757,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Thoughtworks India</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Software Procurement Intern</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3797,7 +3777,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Gurgaon, India; Pune, India</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3807,12 +3787,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3824,17 +3804,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3844,7 +3824,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3854,12 +3834,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3871,17 +3851,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3889,7 +3869,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
@@ -3897,12 +3881,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3911,552 +3895,8 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>AI Video Editor</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>AI Sound Designer</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>AI Animator</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Shipsy</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>QA / SDET</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Shipsy</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Full Stack</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>SirionLabs</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Intern- Employee Engagement</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sirionlabs.com/careers/</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Sprinklr</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Internship and Early Careers</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Stripe India</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Intern</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/stripe</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Thoughtworks India</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Developer (Vapasi) - Intern</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>1–5 years</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Thoughtworks India</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Software Procurement Intern</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Gurgaon, India; Pune, India</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Test Jerin</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I88"/>
+  <autoFilter ref="A1:I76"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4533,18 +3973,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4556,7 +3984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4584,35 +4012,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Cuemath</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://www.cuemath.com/careers/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cuemath</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.cuemath.com/careers/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4621,6 +4029,26 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Exotel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://exotel.com/careers/</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://exotel.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -4644,15 +4072,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Plivo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.plivo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.plivo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4661,18 +4109,78 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vymo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://getvymo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Zluri</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.zluri.com/careers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.zluri.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ideaForge</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://ideaforgetech.com/careers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://ideaforgetech.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4681,18 +4189,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4701,18 +4209,38 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CRED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://careers.cred.club/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://careers.cred.club/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4721,38 +4249,38 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CRED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://careers.cred.club/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Darwinbox</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://darwinbox.com/careers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://careers.cred.club/", waiting until "networkidle"
+  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4761,18 +4289,58 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Juspay</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://juspay.io/careers</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://juspay.io/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LatentView Analytics</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.latentview.com/careers/</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.latentview.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4781,18 +4349,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4801,18 +4369,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>OYO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://www.oyorooms.com/careers/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4821,18 +4389,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4841,18 +4409,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4861,38 +4429,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tata 1mg</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://www.1mg.com/jobs</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.1mg.com/jobs", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4901,18 +4449,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4921,18 +4469,38 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Amazon India</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/locations/india</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.amazon.jobs/en/locations/india", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4941,6 +4509,26 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cigniti Technologies</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.cigniti.com/careers/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.cigniti.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
